--- a/data/trans_dic/P57_AF_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,13; 70,12</t>
+          <t>63,39; 70,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,22; 60,62</t>
+          <t>53,17; 61,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,99; 76,98</t>
+          <t>70,18; 77,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,4; 54,86</t>
+          <t>46,3; 55,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,35; 70,86</t>
+          <t>64,07; 71,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,46; 67,13</t>
+          <t>59,59; 67,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,46; 81,01</t>
+          <t>74,08; 80,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,7; 58,89</t>
+          <t>52,69; 58,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,53; 69,63</t>
+          <t>64,48; 69,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,42; 62,7</t>
+          <t>57,33; 62,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,53; 78,23</t>
+          <t>73,57; 78,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,78; 55,99</t>
+          <t>50,77; 56,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,67; 63,65</t>
+          <t>56,83; 63,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,77; 65,15</t>
+          <t>58,77; 65,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,83; 76,21</t>
+          <t>70,31; 76,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,03; 58,65</t>
+          <t>24,9; 59,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,19; 65,72</t>
+          <t>58,93; 65,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,46; 70,7</t>
+          <t>64,43; 70,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,57; 79,61</t>
+          <t>74,36; 79,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 63,87</t>
+          <t>58,31; 63,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,06; 63,31</t>
+          <t>58,99; 63,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,51; 66,99</t>
+          <t>62,73; 66,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,32; 77,28</t>
+          <t>73,33; 77,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,64; 60,14</t>
+          <t>36,59; 60,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,66; 60,3</t>
+          <t>53,04; 60,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,71; 63,11</t>
+          <t>55,51; 63,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,92; 83,48</t>
+          <t>77,51; 83,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,76; 63,61</t>
+          <t>54,61; 63,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,95; 62,14</t>
+          <t>54,43; 61,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,51; 65,72</t>
+          <t>58,32; 65,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,19; 84,72</t>
+          <t>79,04; 84,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,81; 81,69</t>
+          <t>52,97; 82,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,48; 59,96</t>
+          <t>54,78; 60,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,2; 63,27</t>
+          <t>57,93; 63,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,38; 83,31</t>
+          <t>79,54; 83,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,07; 77,12</t>
+          <t>55,8; 76,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,5; 62,71</t>
+          <t>56,15; 62,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,22; 70,44</t>
+          <t>64,25; 70,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,22; 71,93</t>
+          <t>66,01; 71,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,31; 58,54</t>
+          <t>51,21; 58,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,1; 61,25</t>
+          <t>55,2; 61,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,18; 74,52</t>
+          <t>69,02; 74,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,64; 72,72</t>
+          <t>66,57; 72,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,67; 56,16</t>
+          <t>40,71; 56,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,65; 60,89</t>
+          <t>56,52; 60,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,62; 71,83</t>
+          <t>67,53; 71,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,1; 71,44</t>
+          <t>67,04; 71,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,56; 55,89</t>
+          <t>46,55; 55,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,15; 62,57</t>
+          <t>59,03; 62,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,1; 63,56</t>
+          <t>60,17; 63,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,31; 75,45</t>
+          <t>72,4; 75,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,25; 56,51</t>
+          <t>40,43; 56,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,51; 62,8</t>
+          <t>59,65; 62,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,2; 68,51</t>
+          <t>65,13; 68,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,56; 77,49</t>
+          <t>74,67; 77,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,62; 65,2</t>
+          <t>54,5; 65,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,81; 62,09</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,27; 65,54</t>
+          <t>63,26; 65,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74,01; 76,13</t>
+          <t>73,99; 76,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,44; 58,84</t>
+          <t>49,44; 59,25</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>438102; 486644</t>
+          <t>439944; 491666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>371808; 423514</t>
+          <t>371447; 426518</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>470907; 517921</t>
+          <t>472198; 519715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>291465; 344600</t>
+          <t>290805; 346594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>435418; 487033</t>
+          <t>440382; 488492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>411101; 464133</t>
+          <t>412007; 465242</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>498105; 541910</t>
+          <t>495541; 540096</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>352334; 393714</t>
+          <t>352247; 393175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>891400; 961809</t>
+          <t>890774; 959489</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>798098; 871581</t>
+          <t>796844; 873331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>986650; 1049646</t>
+          <t>987127; 1049384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>658523; 725998</t>
+          <t>658359; 730336</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>544442; 611515</t>
+          <t>546013; 607007</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>595798; 660515</t>
+          <t>595855; 662375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>722667; 777609</t>
+          <t>717371; 778208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>296792; 695541</t>
+          <t>295269; 700215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>573170; 636381</t>
+          <t>570659; 632205</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>661294; 725278</t>
+          <t>660923; 723879</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>773882; 826120</t>
+          <t>771677; 827459</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>552452; 606376</t>
+          <t>553604; 605467</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1139265; 1221350</t>
+          <t>1138045; 1230675</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1274923; 1366413</t>
+          <t>1279595; 1366354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1509043; 1590450</t>
+          <t>1509270; 1592840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>761065; 1284199</t>
+          <t>781264; 1283251</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>356371; 408058</t>
+          <t>358950; 411438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>418057; 473557</t>
+          <t>416570; 474606</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>587809; 629811</t>
+          <t>584767; 628986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>385062; 447347</t>
+          <t>384043; 445264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>375791; 424970</t>
+          <t>372200; 421935</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>453496; 509326</t>
+          <t>452013; 506236</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>615877; 658922</t>
+          <t>614778; 658598</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>491257; 759945</t>
+          <t>492748; 765968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>741239; 815852</t>
+          <t>745278; 816972</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>887774; 965075</t>
+          <t>883710; 966641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1216203; 1276481</t>
+          <t>1218773; 1279127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>915955; 1259807</t>
+          <t>911460; 1247314</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>531451; 589837</t>
+          <t>528117; 585895</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>605553; 664152</t>
+          <t>605836; 664595</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>616834; 670008</t>
+          <t>614853; 669962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>470124; 536356</t>
+          <t>469208; 538508</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>571760; 635593</t>
+          <t>572824; 633149</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>719281; 774817</t>
+          <t>717641; 777637</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>693937; 757345</t>
+          <t>693297; 756072</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>428946; 607215</t>
+          <t>440183; 605960</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1120617; 1204600</t>
+          <t>1118147; 1206274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1340742; 1424166</t>
+          <t>1338846; 1425766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1323759; 1409362</t>
+          <t>1322709; 1402652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>930075; 1116448</t>
+          <t>929815; 1118069</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1935520; 2047449</t>
+          <t>1931499; 2040308</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2047014; 2164819</t>
+          <t>2049151; 2166148</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2443440; 2549433</t>
+          <t>2446255; 2549832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1347645; 1940319</t>
+          <t>1388323; 1943104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2009712; 2120774</t>
+          <t>2014386; 2124563</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2303002; 2419673</t>
+          <t>2300373; 2417984</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2628925; 2732085</t>
+          <t>2632941; 2732581</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1982363; 2366368</t>
+          <t>1978061; 2390665</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3977174; 4128712</t>
+          <t>3970701; 4129880</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4389377; 4546755</t>
+          <t>4388709; 4554484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5110015; 5256477</t>
+          <t>5108940; 5254090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3491972; 4156024</t>
+          <t>3491842; 4185170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AF_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,39; 70,84</t>
+          <t>63,59; 70,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,17; 61,05</t>
+          <t>53,01; 60,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,18; 77,25</t>
+          <t>70,18; 77,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,3; 55,18</t>
+          <t>48,63; 56,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,07; 71,07</t>
+          <t>63,64; 70,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,59; 67,29</t>
+          <t>59,21; 67,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,74</t>
+          <t>74,54; 81,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,69; 58,81</t>
+          <t>52,59; 58,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64,48; 69,46</t>
+          <t>64,5; 69,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,33; 62,83</t>
+          <t>57,74; 62,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,57; 78,21</t>
+          <t>73,35; 78,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,77; 56,32</t>
+          <t>51,69; 56,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,83; 63,18</t>
+          <t>57,17; 63,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,77; 65,33</t>
+          <t>58,88; 65,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,31; 76,27</t>
+          <t>70,7; 76,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 59,04</t>
+          <t>54,28; 61,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,93; 65,28</t>
+          <t>59,16; 65,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,43; 70,56</t>
+          <t>64,54; 70,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,36; 79,73</t>
+          <t>74,38; 79,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,31; 63,77</t>
+          <t>59,59; 65,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,99; 63,79</t>
+          <t>58,7; 63,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,73; 66,99</t>
+          <t>62,79; 66,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,33; 77,39</t>
+          <t>73,23; 77,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,59; 60,1</t>
+          <t>57,96; 62,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,04; 60,8</t>
+          <t>52,61; 60,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,51; 63,25</t>
+          <t>55,73; 63,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,51; 83,37</t>
+          <t>77,34; 83,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,61; 63,32</t>
+          <t>56,39; 64,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,43; 61,7</t>
+          <t>54,64; 61,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,32; 65,32</t>
+          <t>58,27; 65,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,04; 84,68</t>
+          <t>79,36; 84,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,97; 82,34</t>
+          <t>54,93; 61,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,78; 60,05</t>
+          <t>54,76; 60,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57,93; 63,37</t>
+          <t>58,03; 63,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,54; 83,48</t>
+          <t>79,49; 83,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,8; 76,36</t>
+          <t>56,66; 61,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,15; 62,29</t>
+          <t>56,25; 62,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,25; 70,49</t>
+          <t>64,18; 70,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,01; 71,92</t>
+          <t>65,74; 71,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,21; 58,77</t>
+          <t>52,49; 59,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,2; 61,02</t>
+          <t>55,21; 61,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,02; 74,79</t>
+          <t>68,78; 74,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,57; 72,6</t>
+          <t>66,61; 72,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,71; 56,04</t>
+          <t>53,0; 58,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,52; 60,98</t>
+          <t>56,61; 61,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,53; 71,91</t>
+          <t>67,54; 71,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,04; 71,1</t>
+          <t>66,98; 71,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,97</t>
+          <t>53,7; 58,12</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,03; 62,36</t>
+          <t>58,95; 62,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,6</t>
+          <t>60,38; 63,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,4; 75,46</t>
+          <t>72,36; 75,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 56,59</t>
+          <t>54,97; 58,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,65; 62,91</t>
+          <t>59,65; 62,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,13; 68,46</t>
+          <t>65,15; 68,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,67; 77,5</t>
+          <t>74,53; 77,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,5; 65,87</t>
+          <t>56,62; 59,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,76; 62,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,26; 65,65</t>
+          <t>63,18; 65,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,99; 76,09</t>
+          <t>74,07; 76,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,44; 59,25</t>
+          <t>56,41; 58,84</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320299</t>
+          <t>358976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>373127</t>
+          <t>405353</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>693427</t>
+          <t>764329</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>439944; 491666</t>
+          <t>441341; 489741</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>371447; 426518</t>
+          <t>370337; 424962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>472198; 519715</t>
+          <t>472197; 518385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290805; 346594</t>
+          <t>332277; 387975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>440382; 488492</t>
+          <t>437451; 486430</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>412007; 465242</t>
+          <t>409363; 464890</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>495541; 540096</t>
+          <t>498636; 541913</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>352247; 393175</t>
+          <t>381585; 425769</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>890774; 959489</t>
+          <t>890998; 961798</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>796844; 873331</t>
+          <t>802546; 873784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>987127; 1049384</t>
+          <t>984118; 1049974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>658359; 730336</t>
+          <t>728306; 799125</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>542745</t>
+          <t>603514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>580763</t>
+          <t>662152</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1123509</t>
+          <t>1265666</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>546013; 607007</t>
+          <t>549263; 610374</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>595855; 662375</t>
+          <t>596930; 659634</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>717371; 778208</t>
+          <t>721325; 778879</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295269; 700215</t>
+          <t>564496; 639723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>570659; 632205</t>
+          <t>572863; 634996</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>660923; 723879</t>
+          <t>662043; 723567</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>771677; 827459</t>
+          <t>771889; 827991</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>553604; 605467</t>
+          <t>632052; 693210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1138045; 1230675</t>
+          <t>1132304; 1221664</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1279595; 1366354</t>
+          <t>1280729; 1365834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1509270; 1592840</t>
+          <t>1507072; 1588589</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>781264; 1283251</t>
+          <t>1217580; 1309314</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415432</t>
+          <t>484647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>606379</t>
+          <t>469614</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1021811</t>
+          <t>954261</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>358950; 411438</t>
+          <t>356025; 411296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>416570; 474606</t>
+          <t>418153; 474571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>584767; 628986</t>
+          <t>583497; 630033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>384043; 445264</t>
+          <t>451439; 515056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>372200; 421935</t>
+          <t>373642; 421269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>452013; 506236</t>
+          <t>451621; 508955</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>614778; 658598</t>
+          <t>617246; 658924</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>492748; 765968</t>
+          <t>443914; 496082</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>745278; 816972</t>
+          <t>745046; 818877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>883710; 966641</t>
+          <t>885157; 966709</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1218773; 1279127</t>
+          <t>1217906; 1278796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>911460; 1247314</t>
+          <t>911512; 994366</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503298</t>
+          <t>549898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>556520</t>
+          <t>615044</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1059818</t>
+          <t>1164942</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>528117; 585895</t>
+          <t>529017; 587550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>605836; 664595</t>
+          <t>605117; 665068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>614853; 669962</t>
+          <t>612348; 668648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>469208; 538508</t>
+          <t>514293; 580695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>572824; 633149</t>
+          <t>572896; 635836</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>717641; 777637</t>
+          <t>715106; 777338</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>693297; 756072</t>
+          <t>693664; 753578</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>440183; 605960</t>
+          <t>585201; 645754</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1118147; 1206274</t>
+          <t>1119773; 1209643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1338846; 1425766</t>
+          <t>1338989; 1424508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1322709; 1402652</t>
+          <t>1321399; 1404625</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>929815; 1118069</t>
+          <t>1119062; 1211145</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1931499; 2040308</t>
+          <t>1929022; 2039205</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2049151; 2166148</t>
+          <t>2056241; 2169055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2446255; 2549832</t>
+          <t>2444893; 2550717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1388323; 1943104</t>
+          <t>1925935; 2061694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2014386; 2124563</t>
+          <t>2014582; 2123827</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2300373; 2417984</t>
+          <t>2301178; 2417346</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2632941; 2732581</t>
+          <t>2627909; 2732923</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1978061; 2390665</t>
+          <t>2093941; 2208051</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3970701; 4129880</t>
+          <t>3973465; 4136987</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4388709; 4554484</t>
+          <t>4383012; 4554313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5108940; 5254090</t>
+          <t>5114418; 5252865</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3491842; 4185170</t>
+          <t>4062573; 4237959</t>
         </is>
       </c>
     </row>
